--- a/output/pdf_financials_xlsx/AIDX.xlsx
+++ b/output/pdf_financials_xlsx/AIDX.xlsx
@@ -2472,7 +2472,7 @@
         <v>17.291</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>27.728</v>
       </c>
     </row>
     <row r="93">
@@ -5031,7 +5031,11 @@
           <t>Share based payments reserve</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -6060,7 +6064,11 @@
           <t>Translation reserve</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AIDX.xlsx
+++ b/output/pdf_financials_xlsx/AIDX.xlsx
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>7.142</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.411</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>19.162</v>
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>7.142</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.411</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>19.162</v>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>10.183</v>
+        <v>3.041</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.978</v>
+        <v>1.567</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>1.329</v>
@@ -3149,16 +3149,16 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-3.199</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.576</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-1.168</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>0</v>
@@ -3171,16 +3171,16 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-3.199</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.576</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-1.168</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
@@ -11675,7 +11675,11 @@
           <t>Lease payments 18</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -13646,7 +13650,11 @@
           <t>Lease payments 16</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -14821,7 +14829,11 @@
           <t>Lease payments 15</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E282" s="5" t="n">
         <v>-3.199</v>
       </c>

--- a/output/pdf_financials_xlsx/AIDX.xlsx
+++ b/output/pdf_financials_xlsx/AIDX.xlsx
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.484</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.634</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>-1.755</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>-0</v>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-15.541</v>
+        <v>-15.057</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-20.97</v>
+        <v>-20.336</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-31.545</v>
+        <v>-29.79</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-27.48</v>
@@ -1065,7 +1065,7 @@
         <v>7.297</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>16.905</v>
+        <v>5.917</v>
       </c>
     </row>
     <row r="29">
@@ -1075,19 +1075,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-11.232</v>
+        <v>-10.748</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-18.43</v>
+        <v>-17.796</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-28.204</v>
+        <v>-26.449</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-20.183</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-22.213</v>
+        <v>-33.201</v>
       </c>
     </row>
     <row r="30">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-23.48955392433653</v>
+        <v>-22.47736160779639</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-176.8035303146585</v>
+        <v>-170.7214121258634</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-385.4585212518792</v>
+        <v>-361.4732813994807</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-51.78846351226522</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-112.6934199178124</v>
+        <v>-168.4389427223378</v>
       </c>
     </row>
     <row r="31">
@@ -2888,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -12643,7 +12643,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -14298,7 +14302,11 @@
           <t>Loss on disposal of property and equipment 8</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -15585,7 +15593,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -15628,7 +15636,11 @@
           <t>Depreciation of property equipment 9 637</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -18719,7 +18731,11 @@
           <t>Net financing expenses 23</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -19523,7 +19539,11 @@
           <t>Net financing expenses 20</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E396" s="5" t="n">
         <v>0.484</v>
       </c>

--- a/output/pdf_financials_xlsx/AIDX.xlsx
+++ b/output/pdf_financials_xlsx/AIDX.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-15.541</v>
+        <v>-16.288</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-20.97</v>
+        <v>-19.851</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-31.545</v>
+        <v>-32.087</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-27.48</v>
+        <v>-28.336</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-39.118</v>
@@ -779,16 +779,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>0.747</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.119</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>0.542</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>0.856</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -868,10 +868,10 @@
         <v>-15.541</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-20.97</v>
+        <v>-18.195</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-31.545</v>
+        <v>-32.141</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-27.48</v>
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-15.057</v>
+        <v>-15.804</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-20.336</v>
+        <v>-19.217</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-29.79</v>
+        <v>-30.332</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-27.48</v>
+        <v>-28.336</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-39.118</v>
@@ -1075,16 +1075,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-10.748</v>
+        <v>-11.495</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-17.796</v>
+        <v>-16.677</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-26.449</v>
+        <v>-26.991</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-20.183</v>
+        <v>-21.039</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-33.201</v>
@@ -1097,16 +1097,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-22.47736160779639</v>
+        <v>-24.03956751782839</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-170.7214121258634</v>
+        <v>-159.9865694551036</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-361.4732813994807</v>
+        <v>-368.8806888068881</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-51.78846351226522</v>
+        <v>-53.9849122446885</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-168.4389427223378</v>
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-4.586198428290766</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-5.636995617349251</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.689157602767476</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.020892151326934</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -1906,19 +1906,19 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>2.582</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>3.282</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.979</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>4.824</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>9.003</v>
       </c>
     </row>
     <row r="68">
@@ -2982,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-1.221</v>
       </c>
       <c r="F116" s="3" t="n">
         <v>0</v>
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -3290,10 +3290,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.894</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>7.142</v>
@@ -3358,10 +3356,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>7.142</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>1.411</v>
@@ -8494,7 +8490,11 @@
           <t>Deferred tax recovery 25</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -10502,7 +10502,11 @@
           <t>Deferred tax recovery 26</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -11222,7 +11226,11 @@
           <t>Purchase of intangible assets 11</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -14796,7 +14804,11 @@
           <t>Repurchase of shares</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E281" s="5" t="n">
         <v>-0.87</v>
       </c>
@@ -15003,7 +15015,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E286" s="5" t="n">
         <v>0.894</v>
       </c>
@@ -17837,7 +17853,11 @@
           <t>Income taxes recovery 26</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -19055,7 +19075,11 @@
           <t>Income taxes (recovery) expense 24</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -19094,7 +19118,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -19740,7 +19768,11 @@
           <t>Income taxes (recovery) 21</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E401" s="5" t="n">
         <v>-0.747</v>
       </c>
